--- a/data/trans_dic/P43E-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P43E-Clase-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 45,39</t>
+          <t>32,37; 45,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,71; 36,06</t>
+          <t>25,37; 37,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,48; 53,05</t>
+          <t>42,4; 53,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 45,39</t>
+          <t>32,37; 45,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,71; 36,06</t>
+          <t>25,37; 37,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,48; 53,05</t>
+          <t>42,4; 53,18</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,61; 43,95</t>
+          <t>30,98; 44,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,51; 35,02</t>
+          <t>24,12; 35,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,64; 45,92</t>
+          <t>33,53; 44,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,61; 43,95</t>
+          <t>30,98; 44,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,51; 35,02</t>
+          <t>24,12; 35,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,64; 45,92</t>
+          <t>33,53; 44,88</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,99; 35,25</t>
+          <t>21,55; 35,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 20,91</t>
+          <t>7,97; 21,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 39,37</t>
+          <t>22,22; 39,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,99; 35,25</t>
+          <t>21,55; 35,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 20,91</t>
+          <t>7,97; 21,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 39,37</t>
+          <t>22,22; 39,76</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,31; 24,26</t>
+          <t>17,23; 24,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 18,68</t>
+          <t>12,29; 18,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 21,76</t>
+          <t>14,63; 21,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,31; 24,26</t>
+          <t>17,23; 24,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 18,68</t>
+          <t>12,29; 18,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 21,76</t>
+          <t>14,63; 21,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -955,39 +955,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,89; 18,71</t>
+          <t>11,95; 19,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,53</t>
+          <t>3,77; 8,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,24</t>
+          <t>7,33; 12,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,89; 18,71</t>
+          <t>11,95; 19,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,53</t>
+          <t>3,77; 8,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,24</t>
+          <t>7,33; 12,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 19,85</t>
+          <t>13,57; 20,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,63; 15,88</t>
+          <t>9,48; 15,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 16,85</t>
+          <t>10,37; 17,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 19,85</t>
+          <t>13,57; 20,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,63; 15,88</t>
+          <t>9,48; 15,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 16,85</t>
+          <t>10,37; 17,57</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,15; 25,03</t>
+          <t>21,2; 24,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,94; 18,05</t>
+          <t>14,77; 18,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,3; 24,65</t>
+          <t>22,15; 25,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,15; 25,03</t>
+          <t>21,2; 24,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,94; 18,05</t>
+          <t>14,77; 18,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,3; 24,65</t>
+          <t>22,15; 25,77</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110158</t>
+          <t>119240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>110158</t>
+          <t>119240</t>
         </is>
       </c>
     </row>
@@ -1342,32 +1342,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81860; 115286</t>
+          <t>82222; 115114</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65520; 95587</t>
+          <t>67267; 98944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98036; 122427</t>
+          <t>105964; 132899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81860; 115286</t>
+          <t>82222; 115114</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>65520; 95587</t>
+          <t>67267; 98944</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98036; 122427</t>
+          <t>105964; 132899</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81919</t>
+          <t>90760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81919</t>
+          <t>90760</t>
         </is>
       </c>
     </row>
@@ -1460,32 +1460,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84001; 116812</t>
+          <t>82327; 117341</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71918; 102776</t>
+          <t>70797; 103586</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69843; 95331</t>
+          <t>77155; 103269</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84001; 116812</t>
+          <t>82327; 117341</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71918; 102776</t>
+          <t>70797; 103586</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69843; 95331</t>
+          <t>77155; 103269</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>24547</t>
         </is>
       </c>
     </row>
@@ -1578,32 +1578,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36222; 60843</t>
+          <t>37201; 61708</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9459; 23692</t>
+          <t>9036; 24069</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16187; 28939</t>
+          <t>18084; 32366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36222; 60843</t>
+          <t>37201; 61708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9459; 23692</t>
+          <t>9036; 24069</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16187; 28939</t>
+          <t>18084; 32366</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64244</t>
+          <t>70715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64244</t>
+          <t>70715</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93658; 131250</t>
+          <t>93215; 132262</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68008; 101885</t>
+          <t>67019; 101733</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52877; 77945</t>
+          <t>58132; 85575</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93658; 131250</t>
+          <t>93215; 132262</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68008; 101885</t>
+          <t>67019; 101733</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52877; 77945</t>
+          <t>58132; 85575</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>31170</t>
         </is>
       </c>
     </row>
@@ -1814,39 +1814,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56441; 88762</t>
+          <t>56730; 90283</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16133; 36820</t>
+          <t>16272; 37036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16593; 41319</t>
+          <t>23904; 40858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56441; 88762</t>
+          <t>56730; 90283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16133; 36820</t>
+          <t>16272; 37036</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16593; 41319</t>
+          <t>23904; 40858</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>38069</t>
         </is>
       </c>
     </row>
@@ -1932,32 +1932,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73200; 106572</t>
+          <t>72852; 109125</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48004; 79143</t>
+          <t>47236; 77988</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26303; 44232</t>
+          <t>29474; 49953</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73200; 106572</t>
+          <t>72852; 109125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48004; 79143</t>
+          <t>47236; 77988</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26303; 44232</t>
+          <t>29474; 49953</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>342466</t>
+          <t>374501</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>342466</t>
+          <t>374501</t>
         </is>
       </c>
     </row>
@@ -2050,32 +2050,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>474743; 561910</t>
+          <t>476010; 559572</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>320917; 387555</t>
+          <t>317247; 390851</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>296398; 378573</t>
+          <t>347644; 404489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>474743; 561910</t>
+          <t>476010; 559572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>320917; 387555</t>
+          <t>317247; 390851</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>296398; 378573</t>
+          <t>347644; 404489</t>
         </is>
       </c>
     </row>
